--- a/output/roomself_excel/5012.xlsx
+++ b/output/roomself_excel/5012.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>473341</v>
+        <v>102623</v>
       </c>
       <c r="D2" t="n">
-        <v>10352</v>
+        <v>2724</v>
       </c>
       <c r="E2" t="n">
-        <v>838</v>
+        <v>308</v>
       </c>
       <c r="F2" t="n">
-        <v>833</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>270744</v>
+        <v>328718</v>
       </c>
       <c r="D3" t="n">
-        <v>4504</v>
+        <v>5364</v>
       </c>
       <c r="E3" t="n">
-        <v>833</v>
+        <v>849</v>
       </c>
       <c r="F3" t="n">
-        <v>363</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>582006</v>
+        <v>270744</v>
       </c>
       <c r="D4" t="n">
-        <v>11020</v>
+        <v>4504</v>
       </c>
       <c r="E4" t="n">
-        <v>1255</v>
+        <v>833</v>
       </c>
       <c r="F4" t="n">
-        <v>849</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>60204</v>
+        <v>132260</v>
       </c>
       <c r="D6" t="n">
-        <v>2080</v>
+        <v>2952</v>
       </c>
       <c r="E6" t="n">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F6" t="n">
-        <v>273</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79120</v>
+        <v>60204</v>
       </c>
       <c r="D7" t="n">
-        <v>2332</v>
+        <v>2080</v>
       </c>
       <c r="E7" t="n">
-        <v>215</v>
+        <v>413</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         <v>1184</v>
       </c>
       <c r="E9" t="n">
-        <v>849</v>
+        <v>115</v>
       </c>
       <c r="F9" t="n">
-        <v>115</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16810</v>
+        <v>150665</v>
       </c>
       <c r="D11" t="n">
-        <v>1148</v>
+        <v>4796</v>
       </c>
       <c r="E11" t="n">
-        <v>205</v>
+        <v>849</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>164020</v>
+        <v>16810</v>
       </c>
       <c r="D12" t="n">
-        <v>3404</v>
+        <v>1148</v>
       </c>
       <c r="E12" t="n">
-        <v>853</v>
+        <v>205</v>
       </c>
       <c r="F12" t="n">
-        <v>606</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>253659</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="n">
-        <v>4400</v>
+        <v>2332</v>
       </c>
       <c r="E13" t="n">
-        <v>853</v>
+        <v>215</v>
       </c>
       <c r="F13" t="n">
-        <v>493</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55449</v>
+        <v>253659</v>
       </c>
       <c r="D14" t="n">
-        <v>2768</v>
+        <v>4400</v>
       </c>
       <c r="E14" t="n">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="F14" t="n">
-        <v>346</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15">
@@ -778,15 +778,81 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>341081</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7832</v>
+      </c>
+      <c r="E16" t="n">
+        <v>838</v>
+      </c>
+      <c r="F16" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>164020</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3404</v>
+      </c>
+      <c r="E17" t="n">
+        <v>606</v>
+      </c>
+      <c r="F17" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>55449</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2768</v>
+      </c>
+      <c r="E18" t="n">
+        <v>207</v>
+      </c>
+      <c r="F18" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>141955</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D19" t="n">
         <v>3056</v>
       </c>
-      <c r="E16" t="n">
-        <v>853</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="E19" t="n">
+        <v>506</v>
+      </c>
+      <c r="F19" t="n">
         <v>319</v>
       </c>
     </row>

--- a/output/roomself_excel/5012.xlsx
+++ b/output/roomself_excel/5012.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>2724</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>308</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>40</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,31 @@
       <c r="D3" t="n">
         <v>5364</v>
       </c>
-      <c r="E3" t="n">
-        <v>849</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>606</v>
-      </c>
+        <v>859</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>769</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +584,38 @@
       <c r="D4" t="n">
         <v>4504</v>
       </c>
-      <c r="E4" t="n">
-        <v>833</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>363</v>
+        <v>348</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>778</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>348</v>
+      </c>
+      <c r="M4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +633,31 @@
       <c r="D5" t="n">
         <v>2896</v>
       </c>
-      <c r="E5" t="n">
-        <v>418</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>386</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>378</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +674,31 @@
       <c r="D6" t="n">
         <v>2952</v>
       </c>
-      <c r="E6" t="n">
-        <v>410</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>383</v>
       </c>
+      <c r="G6" t="n">
+        <v>28</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>355</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +715,23 @@
       <c r="D7" t="n">
         <v>2080</v>
       </c>
-      <c r="E7" t="n">
-        <v>413</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>273</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +748,23 @@
       <c r="D8" t="n">
         <v>1680</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>206</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>27</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +781,23 @@
       <c r="D9" t="n">
         <v>1184</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>115</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>40</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +814,31 @@
       <c r="D10" t="n">
         <v>1584</v>
       </c>
-      <c r="E10" t="n">
-        <v>255</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>221</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="G10" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>215</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +855,23 @@
       <c r="D11" t="n">
         <v>4796</v>
       </c>
-      <c r="E11" t="n">
-        <v>849</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>221</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="G11" t="n">
+        <v>40</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +888,23 @@
       <c r="D12" t="n">
         <v>1148</v>
       </c>
-      <c r="E12" t="n">
-        <v>205</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
+        <v>187</v>
+      </c>
+      <c r="G12" t="n">
         <v>40</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +921,23 @@
       <c r="D13" t="n">
         <v>2332</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>215</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>27</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +954,31 @@
       <c r="D14" t="n">
         <v>4400</v>
       </c>
-      <c r="E14" t="n">
-        <v>853</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>493</v>
-      </c>
+        <v>658</v>
+      </c>
+      <c r="G14" t="n">
+        <v>41</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>771</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +995,31 @@
       <c r="D15" t="n">
         <v>3556</v>
       </c>
-      <c r="E15" t="n">
-        <v>494</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>486</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="G15" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>444</v>
+      </c>
+      <c r="J15" t="n">
+        <v>41</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1036,31 @@
       <c r="D16" t="n">
         <v>7832</v>
       </c>
-      <c r="E16" t="n">
-        <v>838</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>423</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="G16" t="n">
+        <v>28</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>395</v>
+      </c>
+      <c r="J16" t="n">
+        <v>28</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1077,31 @@
       <c r="D17" t="n">
         <v>3404</v>
       </c>
-      <c r="E17" t="n">
-        <v>606</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>336</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="G17" t="n">
+        <v>41</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>295</v>
+      </c>
+      <c r="J17" t="n">
+        <v>50</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1118,23 @@
       <c r="D18" t="n">
         <v>2768</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>207</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>59</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1151,31 @@
       <c r="D19" t="n">
         <v>3056</v>
       </c>
-      <c r="E19" t="n">
-        <v>506</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>319</v>
       </c>
+      <c r="J19" t="n">
+        <v>41</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
